--- a/info.xlsx
+++ b/info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makal\git\marialarsson.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9850D383-4EF9-4660-B5FA-94E5790E55DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE58040B-5DCC-41E1-BB35-F94D00486C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{6E7444F3-913F-49EF-AA54-6B6F5F9F19BF}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="23980" windowHeight="15260" xr2:uid="{6E7444F3-913F-49EF-AA54-6B6F5F9F19BF}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="372">
   <si>
     <t>doi</t>
   </si>
@@ -1143,6 +1143,12 @@
   </si>
   <si>
     <t>Yuichi Hirose, Maria Larsson, and Takeo Igarashi</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3772318.3791148</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/epdf/10.1145/3772318.3791148</t>
   </si>
 </sst>
 </file>
@@ -1657,8 +1663,13 @@
       <c r="F2" s="6" t="s">
         <v>369</v>
       </c>
+      <c r="G2" s="8" t="s">
+        <v>371</v>
+      </c>
       <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="I2" s="17" t="s">
+        <v>370</v>
+      </c>
       <c r="J2" s="16"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
@@ -2310,9 +2321,11 @@
     <hyperlink ref="I3" r:id="rId27" xr:uid="{4531307F-785D-45AD-BE0C-8BCE95D4D28C}"/>
     <hyperlink ref="G5" r:id="rId28" xr:uid="{B3BA4522-828E-4EC8-9284-9AF6C5A7C791}"/>
     <hyperlink ref="J4" r:id="rId29" xr:uid="{31CFEAD7-A13D-4439-9F4A-98EA840F790B}"/>
+    <hyperlink ref="I2" r:id="rId30" xr:uid="{0B3BA062-2FD3-4E18-A18C-445362E791B0}"/>
+    <hyperlink ref="G2" r:id="rId31" xr:uid="{88A02E64-38AB-44DC-B4DA-BFD07A11719E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
 </worksheet>
 </file>
 
